--- a/docu/공정비트.xlsx
+++ b/docu/공정비트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZEN\Desktop\LYJ\UNITY\project\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F449F23D-F0E1-4E7E-A558-BD9A7DF6E2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6637A211-872E-4359-8951-0551E393E069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="4335" windowWidth="14610" windowHeight="11250" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15975" yWindow="8040" windowWidth="12930" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1차" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="203">
   <si>
     <t>공정 단계 비트</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -462,27 +462,287 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1차 라인 작업 단계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차 불량판정 단계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 라인 이동 및 커버 조립 단계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 불량판정 단계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 공정 이동 단계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M400</t>
+    <t>명령 비트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동운행 시작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 불량판정 실행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료비트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 라인 레인 전진 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 라인 레일 전진 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 1차 라인 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리팩 커버 조립 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 2차 라인 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 2차공정 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M151</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M153</t>
+  </si>
+  <si>
+    <t>M154</t>
+  </si>
+  <si>
+    <t>M155</t>
+  </si>
+  <si>
+    <t>M156</t>
+  </si>
+  <si>
+    <t>M157</t>
+  </si>
+  <si>
+    <t>공정진행단계 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정 1단계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정 2단계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정 3단계</t>
+  </si>
+  <si>
+    <t>공정 3단계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정 4단계</t>
+  </si>
+  <si>
+    <t>공정 5단계</t>
+  </si>
+  <si>
+    <t>공정 6단계</t>
+  </si>
+  <si>
+    <t>공정 7단계</t>
+  </si>
+  <si>
+    <t>공정 8단계</t>
+  </si>
+  <si>
+    <t>공정 9단계</t>
+  </si>
+  <si>
+    <t>공정 10단계</t>
+  </si>
+  <si>
+    <t>공정 11단계</t>
+  </si>
+  <si>
+    <t>공정 12단계</t>
+  </si>
+  <si>
+    <t>공정 13단계</t>
+  </si>
+  <si>
+    <t>공정 14단계</t>
+  </si>
+  <si>
+    <t>공정 15단계</t>
+  </si>
+  <si>
+    <t>공정 16단계</t>
+  </si>
+  <si>
+    <t>공정 17단계</t>
+  </si>
+  <si>
+    <t>M104</t>
+  </si>
+  <si>
+    <t>M105</t>
+  </si>
+  <si>
+    <t>M106</t>
+  </si>
+  <si>
+    <t>M107</t>
+  </si>
+  <si>
+    <t>M108</t>
+  </si>
+  <si>
+    <t>M109</t>
+  </si>
+  <si>
+    <t>M110</t>
+  </si>
+  <si>
+    <t>M111</t>
+  </si>
+  <si>
+    <t>M112</t>
+  </si>
+  <si>
+    <t>M113</t>
+  </si>
+  <si>
+    <t>M114</t>
+  </si>
+  <si>
+    <t>M115</t>
+  </si>
+  <si>
+    <t>M116</t>
+  </si>
+  <si>
+    <t>M117</t>
+  </si>
+  <si>
+    <t>M200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 1차 라인 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리팩 커버 레일 1차 전진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리팩 커버 레일 2차 전진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리팩 커버 조립</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 2차 라인 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 불량판정 실행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 2차 공정 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M203</t>
+  </si>
+  <si>
+    <t>M204</t>
+  </si>
+  <si>
+    <t>M205</t>
+  </si>
+  <si>
+    <t>M206</t>
+  </si>
+  <si>
+    <t>M207</t>
+  </si>
+  <si>
+    <t>M208</t>
+  </si>
+  <si>
+    <t>2차 불량판정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M410</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M411</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M412</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M413</t>
+  </si>
+  <si>
+    <t>M414</t>
+  </si>
+  <si>
+    <t>M415</t>
+  </si>
+  <si>
+    <t>M416</t>
+  </si>
+  <si>
+    <t>공정단계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차라인이동 및 커버조립</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 불량판정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 공정이동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -502,119 +762,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>명령 비트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자동운행 시작</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV 전진 명령</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배터리팩 커버 레일 전진 명령</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차 불량판정 실행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇팔 배터리팩 커버 조립</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 불량판정 실행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV 2차 공정 이동 명령</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료비트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차 라인 레인 전진 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 라인 레일 전진 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV 1차 라인 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배터리팩 커버 조립 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV 2차 라인 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV 2차공정 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M151</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M152</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M153</t>
-  </si>
-  <si>
-    <t>M154</t>
-  </si>
-  <si>
-    <t>M155</t>
-  </si>
-  <si>
-    <t>M156</t>
-  </si>
-  <si>
-    <t>M157</t>
+    <t>순서제어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -645,7 +794,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -668,37 +817,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -710,12 +833,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1020,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D866E9-D9DD-4E2B-AD27-DDF858EE11FA}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.875" style="1" customWidth="1"/>
@@ -1031,225 +1148,304 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>123</v>
+        <v>189</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
+        <v>190</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="2"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="2"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
+      <c r="A11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="6"/>
+        <v>170</v>
+      </c>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="A19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="C20" s="2"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="2"/>
+      <c r="A24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A35:C35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1258,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F19AB3B-DF12-45A0-A24A-C91ABA347E3D}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.625" style="1" customWidth="1"/>
@@ -1830,8 +2026,152 @@
         <v>64</v>
       </c>
     </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A60:C60"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A36:C36"/>

--- a/docu/공정비트.xlsx
+++ b/docu/공정비트.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZEN\Desktop\LYJ\UNITY\project\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6637A211-872E-4359-8951-0551E393E069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FA1987-102C-42BD-AE25-244CCEE9E0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15975" yWindow="8040" windowWidth="12930" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="8835" windowWidth="14610" windowHeight="6750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1차" sheetId="3" r:id="rId1"/>
-    <sheet name="3차" sheetId="2" r:id="rId2"/>
-    <sheet name="2차" sheetId="4" r:id="rId3"/>
+    <sheet name="2차" sheetId="4" r:id="rId2"/>
+    <sheet name="3차" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="267">
   <si>
     <t>공정 단계 비트</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -763,6 +763,262 @@
   </si>
   <si>
     <t>순서제어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M151</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M154</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M157</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정단계 비트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리팩 이동 및 스키드 안착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차 프레임 조립 및 볼트 체결</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불량검사 라인 이동 및 검사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차 공정 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M405</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M406</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M407</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리팩 이송/안착 공정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레임 조립 공정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사 공정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 공정 이송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작 명령 비트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동운행 시작 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 배터리팩 전진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇팔 배터리팩 스키드 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차 프레임 조립</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레임/배터리팩 라인 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스키드 불량검사 라인 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불량검사 실행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M221</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M223</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M225</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M226</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작 완료 비트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV 배터리팩 전진 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리팩 스키드 안착 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차 프레임 조립 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼트 체결 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불량검사 라인 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불량검사 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차 공정 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M161</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M162</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M163</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M164</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순서 제어 비트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇팔 배터리팩 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼트 체결</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불량검사 라인 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M430</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M431</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M433</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M435</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV/스키드 3차 공정 이동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1239,8 +1495,8 @@
       <c r="B13" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
+      <c r="C13" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1250,7 +1506,9 @@
       <c r="B14" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -1259,8 +1517,8 @@
       <c r="B15" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="2">
-        <v>2</v>
+      <c r="C15" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1270,8 +1528,8 @@
       <c r="B16" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="2">
-        <v>3</v>
+      <c r="C16" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1281,8 +1539,8 @@
       <c r="B17" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C17" s="2">
-        <v>4</v>
+      <c r="C17" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1292,8 +1550,8 @@
       <c r="B18" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="2">
-        <v>5</v>
+      <c r="C18" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1303,7 +1561,9 @@
       <c r="B19" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
@@ -1312,7 +1572,9 @@
       <c r="B20" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
@@ -1453,6 +1715,319 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{528F30A2-51E3-4B34-BBF7-3F985B052C1C}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="35.625" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C16" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A29:C29"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F19AB3B-DF12-45A0-A24A-C91ABA347E3D}">
   <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2181,14 +2756,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{528F30A2-51E3-4B34-BBF7-3F985B052C1C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docu/공정비트.xlsx
+++ b/docu/공정비트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZEN\Desktop\LYJ\UNITY\project\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FA1987-102C-42BD-AE25-244CCEE9E0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C76E83-8EB9-41B1-8B46-D27B08D14B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="8835" windowWidth="14610" windowHeight="6750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1차" sheetId="3" r:id="rId1"/>
@@ -1726,294 +1726,302 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>259</v>
       </c>
+      <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>260</v>
       </c>
+      <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>265</v>
       </c>
+      <c r="C36" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2602,147 +2610,164 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>119</v>
       </c>
+      <c r="C61" s="2"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>120</v>
       </c>
+      <c r="C62" s="2"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="C63" s="2"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+      <c r="C76" s="2"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>169</v>
       </c>
+      <c r="C77" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="6">
